--- a/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Prática de Funções de Texto.xlsx
+++ b/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Prática de Funções de Texto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ALUNOS_FIC\LINELSON.ALUNOS\3 - FUNÇÕES DE TEXTO E DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\3 - FUNÇÕES DE TEXTO E DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59FEA87-045A-4126-AF3F-C260F6BE118E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BAD692-09C3-48EF-91C6-68C558F86C06}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXERCÍCIO 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Prática de Funções de Texto</t>
   </si>
@@ -110,6 +110,15 @@
   </si>
   <si>
     <t>Sufixos - 4 Últimos Dígitos</t>
+  </si>
+  <si>
+    <t>DÓLARES</t>
+  </si>
+  <si>
+    <t>PAULO</t>
+  </si>
+  <si>
+    <t>EUGÊNIO</t>
   </si>
 </sst>
 </file>
@@ -509,13 +518,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="1.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="1"/>
@@ -553,7 +562,10 @@
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="str">
+        <f>_xlfn.CONCAT(A3," ",B3," ",C3)</f>
+        <v>Paulo Ricardo da Silva</v>
+      </c>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -566,7 +578,10 @@
       <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="str">
+        <f t="shared" ref="D4:D9" si="0">_xlfn.CONCAT(A4," ",B4," ",C4)</f>
+        <v>Ana Carla de Souza</v>
+      </c>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -579,7 +594,10 @@
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Pedro Sato Camargo</v>
+      </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -592,7 +610,10 @@
       <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Ivo Carlos Figueiras</v>
+      </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -605,7 +626,10 @@
       <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>José Augusto Potato</v>
+      </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -618,21 +642,39 @@
       <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria Dolores Eugênia</v>
+      </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f>PROPER(_xlfn.CONCAT(A9," ",B9," ",C9))</f>
+        <v>Paulo Dólares Eugênio</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -668,60 +710,126 @@
       <c r="A2" s="10">
         <v>1813207762</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="B2" s="8" t="str">
+        <f>MID($A2,1,2)</f>
+        <v>18</v>
+      </c>
+      <c r="C2" s="8" t="str">
+        <f>MID($A2,3,4)</f>
+        <v>1320</v>
+      </c>
+      <c r="D2" s="8" t="str">
+        <f>MID($A2,7,4)</f>
+        <v>7762</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>2330326397</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="B3" s="8" t="str">
+        <f t="shared" ref="B3:B8" si="0">MID($A3,1,2)</f>
+        <v>23</v>
+      </c>
+      <c r="C3" s="8" t="str">
+        <f t="shared" ref="C3:C8" si="1">MID($A3,3,4)</f>
+        <v>3032</v>
+      </c>
+      <c r="D3" s="8" t="str">
+        <f t="shared" ref="D3:D8" si="2">MID($A3,7,4)</f>
+        <v>6397</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>2582509913</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>8250</v>
+      </c>
+      <c r="D4" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>9913</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>1367375569</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="B5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>6737</v>
+      </c>
+      <c r="D5" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>5569</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>1656235421</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="B6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>5623</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>5421</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>2809987281</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="B7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>0998</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>7281</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>1486324125</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="B8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>8632</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>4125</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C2" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>